--- a/Result/profitability/2614.xlsx
+++ b/Result/profitability/2614.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.32</v>
       </c>
       <c r="M2" t="n">
-        <v>0.4337499999999999</v>
+        <v>0.4749999999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>32.93</v>
+        <v>33.19625</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.27</v>
       </c>
       <c r="M3" t="n">
-        <v>0.3749999999999999</v>
+        <v>0.3674999999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>31.0325</v>
+        <v>31.33875</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.27</v>
       </c>
       <c r="M4" t="n">
-        <v>0.335</v>
+        <v>0.3662499999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>30.5975</v>
+        <v>31.2525</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-1.52</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1099999999999999</v>
+        <v>0.1062499999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>22.51125</v>
+        <v>22.44875</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.27</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0737499999999999</v>
+        <v>0.0599999999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>21.2675</v>
+        <v>21.2</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.49</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0549999999999999</v>
+        <v>0.0487499999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>18.745</v>
+        <v>18.7775</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>-1.31</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.1812500000000001</v>
+        <v>-0.1525000000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>16.37625</v>
+        <v>16.985</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1902,7 +1902,7 @@
         <v>-0.1687500000000001</v>
       </c>
       <c r="N12" t="n">
-        <v>6.937499999999999</v>
+        <v>6.937500000000001</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2614</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1306</v>
+      </c>
+      <c r="D75" t="n">
+        <v>852</v>
+      </c>
+      <c r="E75" t="n">
+        <v>454</v>
+      </c>
+      <c r="F75" t="n">
+        <v>34.75</v>
+      </c>
+      <c r="G75" t="n">
+        <v>121</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>9.28%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>62</v>
+      </c>
+      <c r="J75" t="n">
+        <v>184</v>
+      </c>
+      <c r="K75" t="n">
+        <v>174</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.4599999999999999</v>
+      </c>
+      <c r="N75" t="n">
+        <v>33.01125</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.7666666666666668</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>4.870000000000001</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.1629852744310576</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.03000000000000003</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.0535714285714286</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.01418439716312059</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
